--- a/results/Int Task Remove ACC -0.2/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_10_permute.xlsx
@@ -440,127 +440,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6780648254874211</v>
+        <v>0.6759438238943326</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6852497209809835</v>
+        <v>0.6748973467639195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6765515160933515</v>
+        <v>0.6790641415480299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6901548877566539</v>
+        <v>0.6803441386892797</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6939111526996492</v>
+        <v>0.6953862346186352</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6936589344673043</v>
+        <v>0.6850621154918505</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6883334732237313</v>
+        <v>0.6812782187326263</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6870254287502192</v>
+        <v>0.6702998696110687</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6892397136928322</v>
+        <v>0.667646384221028</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6875487711944341</v>
+        <v>0.6616388534084365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6875487711944341</v>
+        <v>0.670766909632742</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6897630561370471</v>
+        <v>0.6490352133217765</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6897630561370471</v>
+        <v>0.6574629172715887</v>
       </c>
     </row>
     <row r="15">
@@ -570,757 +570,757 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.692183229274268</v>
+        <v>0.6542302025308251</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7040954506811554</v>
+        <v>0.650717222225454</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6852873251820168</v>
+        <v>0.645784215875538</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6956862371948347</v>
+        <v>0.6559496078775192</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6919586428581519</v>
+        <v>0.6501382006327479</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6916409808505282</v>
+        <v>0.6350591237764092</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6750947168798402</v>
+        <v>0.6329289808305834</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6728336863834565</v>
+        <v>0.6342526071553523</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6606877372077156</v>
+        <v>0.6358689645257342</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6585012918393482</v>
+        <v>0.6427268489009186</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6584451971748234</v>
+        <v>0.6345422218307137</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.647186998004692</v>
+        <v>0.6378590785682647</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6220081806796679</v>
+        <v>0.6385691954695456</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6220081806796679</v>
+        <v>0.6183132043516163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6225500135873743</v>
+        <v>0.6159867300799535</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6222323515797504</v>
+        <v>0.6140994562557185</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6082269681540202</v>
+        <v>0.6160334756337242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6176539881644413</v>
+        <v>0.6175937383395813</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6013412442045901</v>
+        <v>0.6211160677557065</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5773661768286653</v>
+        <v>0.5925913075707853</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5845099362349095</v>
+        <v>0.5925913075707853</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5845099362349095</v>
+        <v>0.5925913075707853</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5860608498300124</v>
+        <v>0.5929089695784091</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5831829857818724</v>
+        <v>0.5919559835555375</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5650484117730651</v>
+        <v>0.5860604343139788</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5688512145118143</v>
+        <v>0.5844160296113347</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5826324270374621</v>
+        <v>0.5174439863611017</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5940400042216429</v>
+        <v>0.5171169752427237</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5913304241670774</v>
+        <v>0.5109224622150496</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5890787427814477</v>
+        <v>0.5109224622150496</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5910966963982239</v>
+        <v>0.5128751798145634</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5882472951983798</v>
+        <v>0.5138749113912059</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5551454181462501</v>
+        <v>0.5119408920132001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5551454181462501</v>
+        <v>0.5139216569449766</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.56817849405355</v>
+        <v>0.4979822541412405</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5902662876052398</v>
+        <v>0.4979822541412405</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.617062085574696</v>
+        <v>0.4982155663940604</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6090459502560825</v>
+        <v>0.4975428459357961</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.549500632830919</v>
+        <v>0.4958703939008894</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5505190626290697</v>
+        <v>0.49428208386277</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5362145076592071</v>
+        <v>0.4949174078780178</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5486596283790802</v>
+        <v>0.4949174078780178</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5585915003702248</v>
+        <v>0.4949174078780178</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5585915003702248</v>
+        <v>0.4961880559085133</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.540764615984237</v>
+        <v>0.4961880559085133</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5155567125368666</v>
+        <v>0.4961880559085133</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5125855651392021</v>
+        <v>0.497141041931385</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5428201738020465</v>
+        <v>0.497141041931385</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5341122042876268</v>
+        <v>0.497141041931385</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.525264205869912</v>
+        <v>0.4996823379923761</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5240216051716787</v>
+        <v>0.4993927233170146</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5240216051716787</v>
+        <v>0.5003550584506404</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5295433977410886</v>
+        <v>0.5019807649317765</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5430817411451456</v>
+        <v>0.5032981585160426</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5394752697322331</v>
+        <v>0.5013360918057745</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5460528885428102</v>
+        <v>0.5013360918057745</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5495939161804436</v>
+        <v>0.5026628345007949</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5725966760379383</v>
+        <v>0.5023825689361876</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5519482300263521</v>
+        <v>0.5013921864702994</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5450253173919222</v>
+        <v>0.5056807274522301</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5476040098959298</v>
+        <v>0.5047277414293585</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5301789295143532</v>
+        <v>0.5043072392034391</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.545137298962955</v>
+        <v>0.5020368595963012</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5452305823124797</v>
+        <v>0.502345172493171</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5145661223129617</v>
+        <v>0.502345172493171</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5180325648225788</v>
+        <v>0.5017098484779232</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5023732198254335</v>
+        <v>0.5030178929514353</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5000560946645248</v>
+        <v>0.5049799596617034</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5013547900272828</v>
+        <v>0.5030833367267143</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5000093491107541</v>
+        <v>0.5089510463940272</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5000093491107541</v>
+        <v>0.5092687084016511</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5000093491107541</v>
+        <v>0.5054663211789353</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5000093491107541</v>
+        <v>0.49859887993498</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5000093491107541</v>
+        <v>0.4982812179273562</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5003270111183781</v>
+        <v>0.5020275104855471</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.5020275104855471</v>
       </c>
     </row>
   </sheetData>
